--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-26.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H2" t="n">
-        <v>2.14</v>
+        <v>6.6</v>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>4.1</v>
@@ -775,7 +775,7 @@
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.01</v>
@@ -790,7 +790,7 @@
         <v>1.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R2" t="n">
         <v>1.3</v>
@@ -799,16 +799,16 @@
         <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V2" t="n">
         <v>1.14</v>
       </c>
       <c r="W2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X2" t="n">
         <v>21</v>
@@ -817,7 +817,7 @@
         <v>30</v>
       </c>
       <c r="Z2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD2" t="n">
         <v>38</v>
@@ -850,7 +850,7 @@
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -865,19 +865,19 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AU2" t="n">
         <v>2.02</v>
@@ -886,41 +886,41 @@
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -972,10 +972,10 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N3" t="n">
         <v>1.01</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.16</v>
       </c>
       <c r="O3" t="n">
         <v>1.18</v>
@@ -984,10 +984,10 @@
         <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S3" t="n">
         <v>2.32</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>2.74</v>
       </c>
       <c r="H4" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
         <v>2.86</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K4" t="n">
         <v>3.95</v>
@@ -1187,10 +1187,10 @@
         <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V4" t="n">
         <v>1.54</v>
@@ -1202,40 +1202,40 @@
         <v>23</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AA4" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AB4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AC4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>32</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
       </c>
       <c r="AI4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>40</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>46</v>
       </c>
       <c r="AK4" t="n">
         <v>32</v>
@@ -1247,7 +1247,7 @@
         <v>80</v>
       </c>
       <c r="AN4" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AO4" t="n">
         <v>23</v>
@@ -1262,7 +1262,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
@@ -1286,19 +1286,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="BC4" t="n">
         <v>19.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
         <v>16</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
         <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1480,7 +1480,7 @@
         <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
         <v>20</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -1730,10 +1730,10 @@
         <v>2.08</v>
       </c>
       <c r="G7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="I7" t="n">
         <v>1.97</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>3.6</v>
       </c>
       <c r="H11" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I11" t="n">
         <v>2.42</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
         <v>4.1</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
         <v>2.04</v>
@@ -2903,7 +2903,7 @@
         <v>4.6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K13" t="n">
         <v>3.65</v>
@@ -2969,7 +2969,7 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
@@ -2993,13 +2993,13 @@
         <v>85</v>
       </c>
       <c r="AN13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AO13" t="n">
         <v>65</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
         <v>15.5</v>
@@ -3020,7 +3020,7 @@
         <v>16.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AX13" t="n">
         <v>12.5</v>
@@ -3041,7 +3041,7 @@
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE13" t="n">
         <v>36</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4252,10 +4252,10 @@
         <v>3.3</v>
       </c>
       <c r="G20" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="I20" t="n">
         <v>2.24</v>
@@ -4282,7 +4282,7 @@
         <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="R20" t="n">
         <v>1.45</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>2.56</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I21" t="n">
         <v>2.92</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.44</v>
+        <v>2.34</v>
       </c>
       <c r="G22" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I22" t="n">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K22" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>2.12</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -4837,10 +4837,10 @@
         <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
         <v>4.3</v>
@@ -4864,7 +4864,7 @@
         <v>2.56</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5416,16 +5416,16 @@
         <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I26" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J26" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5607,10 +5607,10 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="H27" t="n">
         <v>1.93</v>
@@ -5619,10 +5619,10 @@
         <v>2.22</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,7 +5637,7 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q27" t="n">
         <v>1.6</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5834,7 +5834,7 @@
         <v>2.18</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="G29" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H29" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I29" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.6</v>
       </c>
       <c r="J29" t="n">
         <v>3.9</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q29" t="n">
         <v>1.64</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="G37" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="H37" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="K37" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7747,13 +7747,13 @@
         <v>2.22</v>
       </c>
       <c r="H38" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J38" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K38" t="n">
         <v>3.85</v>
@@ -7798,10 +7798,10 @@
         <v>18</v>
       </c>
       <c r="Y38" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA38" t="n">
         <v>1000</v>
@@ -7816,7 +7816,7 @@
         <v>15</v>
       </c>
       <c r="AE38" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF38" t="n">
         <v>15</v>
@@ -7828,7 +7828,7 @@
         <v>17.5</v>
       </c>
       <c r="AI38" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ38" t="n">
         <v>28</v>
@@ -7849,7 +7849,7 @@
         <v>36</v>
       </c>
       <c r="AP38" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>13</v>
@@ -7858,7 +7858,7 @@
         <v>22</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT38" t="n">
         <v>10</v>
@@ -7882,7 +7882,7 @@
         <v>15</v>
       </c>
       <c r="BA38" t="n">
-        <v>38</v>
+        <v>9.6</v>
       </c>
       <c r="BB38" t="n">
         <v>22</v>
@@ -7894,17 +7894,17 @@
         <v>28</v>
       </c>
       <c r="BE38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG38" t="n">
         <v>29</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -7962,7 +7962,7 @@
         <v>6.8</v>
       </c>
       <c r="O39" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P39" t="n">
         <v>2.92</v>
@@ -8073,7 +8073,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA39" t="n">
         <v>29</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -8162,7 +8162,7 @@
         <v>2.24</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G42" t="n">
         <v>3.15</v>
@@ -8532,7 +8532,7 @@
         <v>2.56</v>
       </c>
       <c r="K42" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.55</v>
+        <v>2.64</v>
       </c>
       <c r="G49" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
         <v>2.22</v>
@@ -9887,10 +9887,10 @@
         <v>2.8</v>
       </c>
       <c r="J49" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -9908,7 +9908,7 @@
         <v>1.76</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G50" t="n">
         <v>2.36</v>
@@ -10078,13 +10078,13 @@
         <v>3.05</v>
       </c>
       <c r="I50" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
         <v>3.7</v>
       </c>
       <c r="K50" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G56" t="n">
         <v>2.44</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11621,7 +11621,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G58" t="n">
         <v>1.72</v>
@@ -11636,7 +11636,7 @@
         <v>3.95</v>
       </c>
       <c r="K58" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
@@ -11651,16 +11651,16 @@
         <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R58" t="n">
         <v>1.36</v>
       </c>
       <c r="S58" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="T58" t="n">
         <v>1.94</v>
@@ -11675,13 +11675,13 @@
         <v>0</v>
       </c>
       <c r="X58" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Y58" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z58" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA58" t="n">
         <v>1000</v>
@@ -11690,7 +11690,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC58" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD58" t="n">
         <v>24</v>
@@ -11735,13 +11735,13 @@
         <v>16</v>
       </c>
       <c r="AR58" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="AS58" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT58" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU58" t="n">
         <v>8.199999999999999</v>
@@ -11750,19 +11750,19 @@
         <v>19.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX58" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY58" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ58" t="n">
         <v>18</v>
       </c>
       <c r="BA58" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB58" t="n">
         <v>14.5</v>
@@ -11774,17 +11774,17 @@
         <v>30</v>
       </c>
       <c r="BE58" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BF58" t="n">
         <v>9.4</v>
       </c>
       <c r="BG58" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -11821,10 +11821,10 @@
         <v>4.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="I59" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J59" t="n">
         <v>3.7</v>
@@ -11848,7 +11848,7 @@
         <v>2.06</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R59" t="n">
         <v>1.4</v>
@@ -11857,7 +11857,7 @@
         <v>3.25</v>
       </c>
       <c r="T59" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U59" t="n">
         <v>2.16</v>
@@ -11893,7 +11893,7 @@
         <v>24</v>
       </c>
       <c r="AF59" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG59" t="n">
         <v>20</v>
@@ -11902,7 +11902,7 @@
         <v>20</v>
       </c>
       <c r="AI59" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AJ59" t="n">
         <v>110</v>
@@ -11917,13 +11917,13 @@
         <v>1000</v>
       </c>
       <c r="AN59" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AO59" t="n">
         <v>15.5</v>
       </c>
       <c r="AP59" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ59" t="n">
         <v>8.6</v>
@@ -11947,7 +11947,7 @@
         <v>18</v>
       </c>
       <c r="AX59" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY59" t="n">
         <v>15</v>
@@ -11956,29 +11956,29 @@
         <v>16</v>
       </c>
       <c r="BA59" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB59" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC59" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC59" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD59" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE59" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF59" t="n">
         <v>7.8</v>
-      </c>
-      <c r="BF59" t="n">
-        <v>7.2</v>
       </c>
       <c r="BG59" t="n">
         <v>11.5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -12039,13 +12039,13 @@
         <v>1.23</v>
       </c>
       <c r="P60" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q60" t="n">
         <v>1.69</v>
       </c>
       <c r="R60" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="S60" t="n">
         <v>2.74</v>
@@ -12054,7 +12054,7 @@
         <v>1.93</v>
       </c>
       <c r="U60" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
@@ -12084,7 +12084,7 @@
         <v>34</v>
       </c>
       <c r="AE60" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF60" t="n">
         <v>9.199999999999999</v>
@@ -12165,14 +12165,14 @@
         <v>10.5</v>
       </c>
       <c r="BF60" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG60" t="n">
         <v>10.5</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G61" t="n">
         <v>1.43</v>
       </c>
       <c r="H61" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I61" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="J61" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K61" t="n">
         <v>5.4</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5.5</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12227,22 +12227,22 @@
         <v>1.03</v>
       </c>
       <c r="N61" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O61" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P61" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q61" t="n">
         <v>1.57</v>
       </c>
       <c r="R61" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="S61" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T61" t="n">
         <v>1.84</v>
@@ -12257,10 +12257,10 @@
         <v>0</v>
       </c>
       <c r="X61" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y61" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z61" t="n">
         <v>1000</v>
@@ -12269,7 +12269,7 @@
         <v>1000</v>
       </c>
       <c r="AB61" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC61" t="n">
         <v>12.5</v>
@@ -12296,7 +12296,7 @@
         <v>12</v>
       </c>
       <c r="AK61" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL61" t="n">
         <v>34</v>
@@ -12305,13 +12305,13 @@
         <v>1000</v>
       </c>
       <c r="AN61" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AO61" t="n">
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ61" t="n">
         <v>29</v>
@@ -12320,7 +12320,7 @@
         <v>34</v>
       </c>
       <c r="AS61" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT61" t="n">
         <v>10.5</v>
@@ -12332,7 +12332,7 @@
         <v>24</v>
       </c>
       <c r="AW61" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX61" t="n">
         <v>8.6</v>
@@ -12344,7 +12344,7 @@
         <v>20</v>
       </c>
       <c r="BA61" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="BB61" t="n">
         <v>10.5</v>
@@ -12353,7 +12353,7 @@
         <v>12</v>
       </c>
       <c r="BD61" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BE61" t="n">
         <v>38</v>
@@ -12362,11 +12362,11 @@
         <v>4.6</v>
       </c>
       <c r="BG61" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -12400,13 +12400,13 @@
         <v>2.04</v>
       </c>
       <c r="G62" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="H62" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I62" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J62" t="n">
         <v>3.6</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -12597,7 +12597,7 @@
         <v>4.6</v>
       </c>
       <c r="H63" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I63" t="n">
         <v>2.76</v>
@@ -12606,7 +12606,7 @@
         <v>2.36</v>
       </c>
       <c r="K63" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13573,7 @@
         <v>2.34</v>
       </c>
       <c r="J68" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="K68" t="n">
         <v>3.8</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -14176,7 +14176,7 @@
         <v>2.02</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R71" t="n">
         <v>1.39</v>
@@ -14200,10 +14200,10 @@
         <v>21</v>
       </c>
       <c r="Y71" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="Z71" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AA71" t="n">
         <v>12.5</v>
@@ -14248,7 +14248,7 @@
         <v>1000</v>
       </c>
       <c r="AO71" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AP71" t="n">
         <v>15</v>
@@ -14263,7 +14263,7 @@
         <v>9.4</v>
       </c>
       <c r="AT71" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="AU71" t="n">
         <v>10.5</v>
@@ -14275,38 +14275,38 @@
         <v>14</v>
       </c>
       <c r="AX71" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY71" t="n">
         <v>5.7</v>
       </c>
-      <c r="AY71" t="n">
-        <v>5.3</v>
-      </c>
       <c r="AZ71" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA71" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BB71" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC71" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BD71" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE71" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF71" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG71" t="n">
         <v>5.8</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>3.25</v>
       </c>
       <c r="G74" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="H74" t="n">
         <v>2.04</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15122,10 +15122,10 @@
         <v>3.75</v>
       </c>
       <c r="I76" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J76" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="K76" t="n">
         <v>5.2</v>
@@ -15146,7 +15146,7 @@
         <v>1.46</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15307,22 +15307,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G77" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="H77" t="n">
-        <v>2.68</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J77" t="n">
         <v>3.25</v>
       </c>
       <c r="K77" t="n">
-        <v>5.5</v>
+        <v>3.75</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
         <v>6.8</v>
       </c>
       <c r="I78" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J78" t="n">
         <v>4.8</v>
@@ -15531,13 +15531,13 @@
         <v>1.15</v>
       </c>
       <c r="P78" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="R78" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="S78" t="n">
         <v>2.2</v>
@@ -15600,25 +15600,25 @@
         <v>26</v>
       </c>
       <c r="AM78" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AN78" t="n">
         <v>5.3</v>
       </c>
       <c r="AO78" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP78" t="n">
         <v>25</v>
       </c>
       <c r="AQ78" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="AR78" t="n">
         <v>10</v>
       </c>
       <c r="AS78" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT78" t="n">
         <v>12</v>
@@ -15630,7 +15630,7 @@
         <v>21</v>
       </c>
       <c r="AW78" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX78" t="n">
         <v>10.5</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15695,16 +15695,16 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G79" t="n">
         <v>3.3</v>
       </c>
       <c r="H79" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I79" t="n">
         <v>2.58</v>
-      </c>
-      <c r="I79" t="n">
-        <v>2.62</v>
       </c>
       <c r="J79" t="n">
         <v>3.25</v>
@@ -15725,7 +15725,7 @@
         <v>1.34</v>
       </c>
       <c r="P79" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q79" t="n">
         <v>2.06</v>
@@ -15740,7 +15740,7 @@
         <v>1.78</v>
       </c>
       <c r="U79" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V79" t="n">
         <v>0</v>
@@ -15764,7 +15764,7 @@
         <v>13</v>
       </c>
       <c r="AC79" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD79" t="n">
         <v>12.5</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -15892,13 +15892,13 @@
         <v>4.6</v>
       </c>
       <c r="G80" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="H80" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="I80" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="J80" t="n">
         <v>3.45</v>
@@ -15919,7 +15919,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q80" t="n">
         <v>2.06</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -16277,19 +16277,19 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G82" t="n">
         <v>2.16</v>
       </c>
       <c r="H82" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="I82" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="J82" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K82" t="n">
         <v>3.75</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -16501,7 +16501,7 @@
         <v>0</v>
       </c>
       <c r="P83" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="Q83" t="n">
         <v>2.26</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -16862,7 +16862,7 @@
         <v>21</v>
       </c>
       <c r="G85" t="n">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="H85" t="n">
         <v>1.13</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -17053,19 +17053,19 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G86" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="H86" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="I86" t="n">
         <v>1000</v>
       </c>
       <c r="J86" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K86" t="n">
         <v>1000</v>
@@ -17083,7 +17083,7 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="Q86" t="n">
         <v>2.36</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -17635,19 +17635,19 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G89" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="H89" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="I89" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="J89" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K89" t="n">
         <v>3.3</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.07</v>
+        <v>1.56</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -18808,7 +18808,7 @@
         <v>2.34</v>
       </c>
       <c r="I95" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>3.3</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19381,7 +19381,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.71</v>
+        <v>1.23</v>
       </c>
       <c r="G98" t="n">
         <v>2.44</v>
@@ -19390,13 +19390,13 @@
         <v>3.85</v>
       </c>
       <c r="I98" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J98" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="K98" t="n">
-        <v>4.3</v>
+        <v>950</v>
       </c>
       <c r="L98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19575,10 +19575,10 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G99" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H99" t="n">
         <v>1.71</v>
@@ -19590,7 +19590,7 @@
         <v>3.65</v>
       </c>
       <c r="K99" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19608,7 +19608,7 @@
         <v>2.44</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -19963,22 +19963,22 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="G101" t="n">
-        <v>2.7</v>
+        <v>2.58</v>
       </c>
       <c r="H101" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
       <c r="J101" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="K101" t="n">
-        <v>4.8</v>
+        <v>3.4</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -20748,7 +20748,7 @@
         <v>2.02</v>
       </c>
       <c r="I105" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J105" t="n">
         <v>3.35</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -20963,10 +20963,10 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-24 01:12:15</t>
+          <t>2026-04-24 03:45:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-26.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-26.xlsx
@@ -775,25 +775,25 @@
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="O2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S2" t="n">
         <v>2.96</v>
@@ -868,7 +868,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.22</v>
+        <v>15.5</v>
       </c>
       <c r="AR2" t="n">
         <v>2.34</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -987,10 +987,10 @@
         <v>1.71</v>
       </c>
       <c r="R3" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S3" t="n">
-        <v>2.32</v>
+        <v>1.71</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="G4" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H4" t="n">
         <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1178,7 +1178,7 @@
         <v>2.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>1.5</v>
@@ -1187,16 +1187,16 @@
         <v>2.84</v>
       </c>
       <c r="T4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="U4" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V4" t="n">
         <v>1.54</v>
       </c>
       <c r="W4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X4" t="n">
         <v>23</v>
@@ -1226,7 +1226,7 @@
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH4" t="n">
         <v>18</v>
@@ -1235,13 +1235,13 @@
         <v>36</v>
       </c>
       <c r="AJ4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AM4" t="n">
         <v>80</v>
@@ -1262,7 +1262,7 @@
         <v>18</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AT4" t="n">
         <v>12</v>
@@ -1274,7 +1274,7 @@
         <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AX4" t="n">
         <v>17</v>
@@ -1286,19 +1286,19 @@
         <v>13.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BC4" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF4" t="n">
         <v>16</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -1348,16 +1348,16 @@
         <v>3.65</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
         <v>3.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
@@ -1369,13 +1369,13 @@
         <v>1.2</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R5" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
         <v>2.52</v>
@@ -1384,13 +1384,13 @@
         <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="V5" t="n">
         <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X5" t="n">
         <v>24</v>
@@ -1438,7 +1438,7 @@
         <v>34</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN5" t="n">
         <v>12</v>
@@ -1468,7 +1468,7 @@
         <v>13.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX5" t="n">
         <v>12.5</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.93</v>
       </c>
       <c r="G6" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
         <v>1.77</v>
@@ -1545,158 +1545,158 @@
         <v>2.12</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>1.9</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P6" t="n">
         <v>1.85</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="I7" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="J7" t="n">
         <v>3.6</v>
@@ -1745,16 +1745,16 @@
         <v>950</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>1.94</v>
@@ -1763,134 +1763,134 @@
         <v>1.7</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -1930,13 +1930,13 @@
         <v>2.02</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.5</v>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H9" t="n">
-        <v>2.8</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
         <v>500</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q9" t="n">
         <v>1.47</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -2506,10 +2506,10 @@
         <v>3.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H11" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="I11" t="n">
         <v>2.42</v>
@@ -2518,7 +2518,7 @@
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.04</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
         <v>4.6</v>
@@ -2906,7 +2906,7 @@
         <v>3.5</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2969,7 +2969,7 @@
         <v>55</v>
       </c>
       <c r="AF13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
@@ -3002,7 +3002,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AR13" t="n">
         <v>21</v>
@@ -3041,7 +3041,7 @@
         <v>18</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE13" t="n">
         <v>36</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>3.6</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I14" t="n">
         <v>3.25</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="G15" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8</v>
+        <v>2.34</v>
       </c>
       <c r="I15" t="n">
         <v>3.65</v>
       </c>
       <c r="J15" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G16" t="n">
         <v>2.32</v>
@@ -3485,7 +3485,7 @@
         <v>3.95</v>
       </c>
       <c r="J16" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K16" t="n">
         <v>4</v>
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="Q16" t="n">
         <v>1.88</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G17" t="n">
         <v>2.48</v>
@@ -3679,10 +3679,10 @@
         <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>2.52</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -3861,10 +3861,10 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="G18" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="H18" t="n">
         <v>1.04</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.42</v>
+        <v>2.58</v>
       </c>
       <c r="Q18" t="n">
         <v>1.38</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
         <v>3.6</v>
       </c>
       <c r="J19" t="n">
-        <v>2.52</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
         <v>6.2</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -4255,13 +4255,13 @@
         <v>4.1</v>
       </c>
       <c r="H20" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="I20" t="n">
         <v>2.24</v>
       </c>
       <c r="J20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K20" t="n">
         <v>4.5</v>
@@ -4282,13 +4282,13 @@
         <v>2.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="T20" t="n">
         <v>1.01</v>
@@ -4300,7 +4300,7 @@
         <v>1.8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>2.72</v>
       </c>
       <c r="I21" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>4.1</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="G22" t="n">
         <v>2.48</v>
       </c>
       <c r="H22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I22" t="n">
         <v>3.35</v>
       </c>
       <c r="J22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>1.81</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
         <v>4.9</v>
@@ -4846,7 +4846,7 @@
         <v>4.3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G24" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H24" t="n">
         <v>3.9</v>
@@ -5040,7 +5040,7 @@
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="G25" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H25" t="n">
-        <v>3.2</v>
+        <v>1.71</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>2.56</v>
+        <v>1.71</v>
       </c>
       <c r="K25" t="n">
-        <v>6.2</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -5416,13 +5416,13 @@
         <v>3.7</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="H26" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="I26" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="J26" t="n">
         <v>3.55</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G27" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H27" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="I27" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="J27" t="n">
         <v>3.35</v>
       </c>
       <c r="K27" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="G28" t="n">
         <v>6.4</v>
       </c>
       <c r="H28" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I28" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="J28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>2.34</v>
       </c>
       <c r="H29" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I29" t="n">
         <v>3.25</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q29" t="n">
         <v>1.64</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>2.08</v>
       </c>
       <c r="H30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I30" t="n">
         <v>3.7</v>
@@ -6204,7 +6204,7 @@
         <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6219,7 +6219,7 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q30" t="n">
         <v>1.57</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G31" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H31" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="I31" t="n">
         <v>1000</v>
       </c>
       <c r="J31" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K31" t="n">
         <v>1000</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.34</v>
+        <v>2.52</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.69</v>
+        <v>1.4</v>
       </c>
       <c r="G32" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="J32" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="Q32" t="n">
         <v>1.76</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6771,22 +6771,22 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G33" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H33" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I33" t="n">
         <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K33" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,7 +6801,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1.87</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="Q34" t="n">
         <v>1.92</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G35" t="n">
         <v>5.1</v>
@@ -7168,10 +7168,10 @@
         <v>1.81</v>
       </c>
       <c r="I35" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J35" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
         <v>4.1</v>
@@ -7195,7 +7195,7 @@
         <v>2.08</v>
       </c>
       <c r="R35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S35" t="n">
         <v>3.85</v>
@@ -7264,7 +7264,7 @@
         <v>120</v>
       </c>
       <c r="AO35" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP35" t="n">
         <v>12.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="G36" t="n">
-        <v>3.25</v>
+        <v>2.86</v>
       </c>
       <c r="H36" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I36" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J36" t="n">
         <v>3.4</v>
       </c>
       <c r="K36" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -7553,16 +7553,16 @@
         <v>2.48</v>
       </c>
       <c r="H37" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I37" t="n">
         <v>4.7</v>
       </c>
       <c r="J37" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K37" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -7741,13 +7741,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G38" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H38" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="I38" t="n">
         <v>3.55</v>
@@ -7774,7 +7774,7 @@
         <v>2.18</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="R38" t="n">
         <v>1.44</v>
@@ -7858,7 +7858,7 @@
         <v>22</v>
       </c>
       <c r="AS38" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="AT38" t="n">
         <v>10</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -7935,7 +7935,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G39" t="n">
         <v>1.59</v>
@@ -7947,10 +7947,10 @@
         <v>6.8</v>
       </c>
       <c r="J39" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K39" t="n">
         <v>4.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.7</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
         <v>2.92</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R39" t="n">
         <v>1.8</v>
@@ -8019,7 +8019,7 @@
         <v>11</v>
       </c>
       <c r="AH39" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AI39" t="n">
         <v>1000</v>
@@ -8034,7 +8034,7 @@
         <v>26</v>
       </c>
       <c r="AM39" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN39" t="n">
         <v>5.3</v>
@@ -8058,10 +8058,10 @@
         <v>12.5</v>
       </c>
       <c r="AU39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AV39" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW39" t="n">
         <v>32</v>
@@ -8094,11 +8094,11 @@
         <v>4.9</v>
       </c>
       <c r="BG39" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
         <v>1000</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>1.27</v>
       </c>
       <c r="I40" t="n">
         <v>2.16</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G41" t="n">
         <v>4.5</v>
@@ -8332,13 +8332,13 @@
         <v>2.1</v>
       </c>
       <c r="I41" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="K41" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -8353,10 +8353,10 @@
         <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G42" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="H42" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I42" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J42" t="n">
         <v>3.4</v>
       </c>
-      <c r="J42" t="n">
-        <v>2.56</v>
-      </c>
       <c r="K42" t="n">
-        <v>6.4</v>
+        <v>4.1</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -8547,10 +8547,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>1.95</v>
+        <v>2.16</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q43" t="n">
         <v>1.34</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="G45" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I45" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J45" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K45" t="n">
-        <v>9</v>
+        <v>4.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
@@ -9132,13 +9132,13 @@
         <v>2.28</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="R45" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S45" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="T45" t="n">
         <v>1.01</v>
@@ -9150,7 +9150,7 @@
         <v>1.23</v>
       </c>
       <c r="W45" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>1000</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>3.45</v>
       </c>
       <c r="H46" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I46" t="n">
         <v>2.38</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9487,7 +9487,7 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="G47" t="n">
         <v>2.18</v>
@@ -9502,7 +9502,7 @@
         <v>3.4</v>
       </c>
       <c r="K47" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -9517,10 +9517,10 @@
         <v>0</v>
       </c>
       <c r="P47" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9681,13 +9681,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G48" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="H48" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>1000</v>
@@ -9696,7 +9696,7 @@
         <v>3.75</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.96</v>
+        <v>2.1</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="G49" t="n">
         <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="J49" t="n">
-        <v>2.54</v>
+        <v>2.98</v>
       </c>
       <c r="K49" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q49" t="n">
         <v>1.87</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>2.04</v>
       </c>
       <c r="G50" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I50" t="n">
         <v>4.2</v>
@@ -10084,7 +10084,7 @@
         <v>3.7</v>
       </c>
       <c r="K50" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -10266,19 +10266,19 @@
         <v>2.3</v>
       </c>
       <c r="G51" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H51" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="I51" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J51" t="n">
         <v>3.7</v>
       </c>
-      <c r="J51" t="n">
-        <v>2.62</v>
-      </c>
       <c r="K51" t="n">
-        <v>5.9</v>
+        <v>5.2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -10487,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -10651,22 +10651,22 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G53" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H53" t="n">
-        <v>3.05</v>
+        <v>2.78</v>
       </c>
       <c r="I53" t="n">
         <v>4.3</v>
       </c>
       <c r="J53" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="K53" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10681,7 +10681,7 @@
         <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
         <v>1.68</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -10851,13 +10851,13 @@
         <v>1000</v>
       </c>
       <c r="H54" t="n">
-        <v>1.04</v>
+        <v>1.25</v>
       </c>
       <c r="I54" t="n">
         <v>1.97</v>
       </c>
       <c r="J54" t="n">
-        <v>2.02</v>
+        <v>3.85</v>
       </c>
       <c r="K54" t="n">
         <v>1000</v>
@@ -10875,10 +10875,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -11039,19 +11039,19 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G55" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="H55" t="n">
-        <v>2.78</v>
+        <v>1.09</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K55" t="n">
         <v>950</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -11245,10 +11245,10 @@
         <v>3.6</v>
       </c>
       <c r="J56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K56" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="G57" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="H57" t="n">
-        <v>2.5</v>
+        <v>2.66</v>
       </c>
       <c r="I57" t="n">
         <v>3.6</v>
       </c>
       <c r="J57" t="n">
-        <v>2.5</v>
+        <v>3.45</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11460,7 +11460,7 @@
         <v>2.02</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -11621,19 +11621,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G58" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H58" t="n">
         <v>5.8</v>
       </c>
       <c r="I58" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J58" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K58" t="n">
         <v>4.2</v>
@@ -11654,7 +11654,7 @@
         <v>1.94</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R58" t="n">
         <v>1.36</v>
@@ -11690,7 +11690,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC58" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD58" t="n">
         <v>24</v>
@@ -11735,7 +11735,7 @@
         <v>16</v>
       </c>
       <c r="AR58" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AS58" t="n">
         <v>7.4</v>
@@ -11750,7 +11750,7 @@
         <v>19.5</v>
       </c>
       <c r="AW58" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX58" t="n">
         <v>8.800000000000001</v>
@@ -11762,7 +11762,7 @@
         <v>18</v>
       </c>
       <c r="BA58" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB58" t="n">
         <v>14.5</v>
@@ -11774,17 +11774,17 @@
         <v>30</v>
       </c>
       <c r="BE58" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF58" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG58" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -11821,7 +11821,7 @@
         <v>4.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="I59" t="n">
         <v>1.99</v>
@@ -11908,16 +11908,16 @@
         <v>110</v>
       </c>
       <c r="AK59" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AL59" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM59" t="n">
         <v>1000</v>
       </c>
       <c r="AN59" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO59" t="n">
         <v>15.5</v>
@@ -11962,7 +11962,7 @@
         <v>8.4</v>
       </c>
       <c r="BC59" t="n">
-        <v>7.8</v>
+        <v>44</v>
       </c>
       <c r="BD59" t="n">
         <v>8</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12203,16 +12203,16 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G61" t="n">
         <v>1.43</v>
       </c>
       <c r="H61" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J61" t="n">
         <v>5.3</v>
@@ -12233,10 +12233,10 @@
         <v>1.18</v>
       </c>
       <c r="P61" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R61" t="n">
         <v>1.66</v>
@@ -12248,7 +12248,7 @@
         <v>1.84</v>
       </c>
       <c r="U61" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
@@ -12281,7 +12281,7 @@
         <v>120</v>
       </c>
       <c r="AF61" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG61" t="n">
         <v>11</v>
@@ -12305,7 +12305,7 @@
         <v>1000</v>
       </c>
       <c r="AN61" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AO61" t="n">
         <v>1000</v>
@@ -12320,7 +12320,7 @@
         <v>34</v>
       </c>
       <c r="AS61" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT61" t="n">
         <v>10.5</v>
@@ -12332,7 +12332,7 @@
         <v>24</v>
       </c>
       <c r="AW61" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX61" t="n">
         <v>8.6</v>
@@ -12344,7 +12344,7 @@
         <v>20</v>
       </c>
       <c r="BA61" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB61" t="n">
         <v>10.5</v>
@@ -12359,14 +12359,14 @@
         <v>38</v>
       </c>
       <c r="BF61" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG61" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12400,19 +12400,19 @@
         <v>2.04</v>
       </c>
       <c r="G62" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="H62" t="n">
         <v>3.45</v>
       </c>
       <c r="I62" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="J62" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K62" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G63" t="n">
         <v>4.6</v>
       </c>
       <c r="H63" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I63" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="J63" t="n">
-        <v>2.36</v>
+        <v>3.2</v>
       </c>
       <c r="K63" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -12624,7 +12624,7 @@
         <v>1.83</v>
       </c>
       <c r="Q63" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="G64" t="n">
         <v>8.6</v>
@@ -12800,7 +12800,7 @@
         <v>5.1</v>
       </c>
       <c r="K64" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="G65" t="n">
         <v>3.95</v>
@@ -12991,10 +12991,10 @@
         <v>3.05</v>
       </c>
       <c r="J65" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="K65" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -13182,13 +13182,13 @@
         <v>3.2</v>
       </c>
       <c r="I66" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J66" t="n">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="K66" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
@@ -13203,7 +13203,7 @@
         <v>0</v>
       </c>
       <c r="P66" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q66" t="n">
         <v>2.08</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -13561,22 +13561,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G68" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="H68" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="I68" t="n">
-        <v>2.34</v>
+        <v>60</v>
       </c>
       <c r="J68" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="K68" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -13755,22 +13755,22 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G69" t="n">
         <v>3.8</v>
       </c>
       <c r="H69" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="I69" t="n">
         <v>3.4</v>
       </c>
       <c r="J69" t="n">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="K69" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         <v>1.63</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="R69" t="n">
         <v>0</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -13949,22 +13949,22 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="G70" t="n">
         <v>3.95</v>
       </c>
       <c r="H70" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="I70" t="n">
         <v>2.96</v>
       </c>
       <c r="J70" t="n">
-        <v>2.44</v>
+        <v>3.15</v>
       </c>
       <c r="K70" t="n">
-        <v>5.8</v>
+        <v>4.6</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -13979,10 +13979,10 @@
         <v>0</v>
       </c>
       <c r="P70" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q70" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R70" t="n">
         <v>0</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -14146,16 +14146,16 @@
         <v>11</v>
       </c>
       <c r="G71" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="H71" t="n">
         <v>1.35</v>
       </c>
       <c r="I71" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="J71" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="K71" t="n">
         <v>5.7</v>
@@ -14179,7 +14179,7 @@
         <v>1.84</v>
       </c>
       <c r="R71" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S71" t="n">
         <v>3.15</v>
@@ -14188,10 +14188,10 @@
         <v>2.28</v>
       </c>
       <c r="U71" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="V71" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="W71" t="n">
         <v>1.09</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -14537,16 +14537,16 @@
         <v>4.8</v>
       </c>
       <c r="H73" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="I73" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="J73" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K73" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="L73" t="n">
         <v>1.01</v>
@@ -14555,7 +14555,7 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="O73" t="n">
         <v>1.13</v>
@@ -14564,10 +14564,10 @@
         <v>2.38</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="R73" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S73" t="n">
         <v>2</v>
@@ -14579,7 +14579,7 @@
         <v>1.01</v>
       </c>
       <c r="V73" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="W73" t="n">
         <v>1.26</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -14728,10 +14728,10 @@
         <v>3.25</v>
       </c>
       <c r="G74" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="H74" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="I74" t="n">
         <v>2.32</v>
@@ -14755,7 +14755,7 @@
         <v>0</v>
       </c>
       <c r="P74" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q74" t="n">
         <v>1.67</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14919,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="G75" t="n">
         <v>1.95</v>
@@ -14952,7 +14952,7 @@
         <v>1.05</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.58</v>
+        <v>1.02</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -15116,7 +15116,7 @@
         <v>1.85</v>
       </c>
       <c r="G76" t="n">
-        <v>1000</v>
+        <v>2.38</v>
       </c>
       <c r="H76" t="n">
         <v>3.75</v>
@@ -15125,10 +15125,10 @@
         <v>6.4</v>
       </c>
       <c r="J76" t="n">
-        <v>1.18</v>
+        <v>2.98</v>
       </c>
       <c r="K76" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G77" t="n">
         <v>2.62</v>
@@ -15316,7 +15316,7 @@
         <v>3</v>
       </c>
       <c r="I77" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="J77" t="n">
         <v>3.25</v>
@@ -15340,7 +15340,7 @@
         <v>1.71</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
         <v>6.8</v>
       </c>
       <c r="I78" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J78" t="n">
         <v>4.8</v>
@@ -15534,10 +15534,10 @@
         <v>2.88</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R78" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="S78" t="n">
         <v>2.2</v>
@@ -15609,7 +15609,7 @@
         <v>1000</v>
       </c>
       <c r="AP78" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ78" t="n">
         <v>9</v>
@@ -15657,14 +15657,14 @@
         <v>10</v>
       </c>
       <c r="BF78" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG78" t="n">
         <v>42</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -15725,7 +15725,7 @@
         <v>1.34</v>
       </c>
       <c r="P79" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q79" t="n">
         <v>2.06</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="G80" t="n">
         <v>5.1</v>
@@ -15898,7 +15898,7 @@
         <v>1.88</v>
       </c>
       <c r="I80" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J80" t="n">
         <v>3.45</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -16095,7 +16095,7 @@
         <v>1000</v>
       </c>
       <c r="J81" t="n">
-        <v>1.92</v>
+        <v>3.25</v>
       </c>
       <c r="K81" t="n">
         <v>1000</v>
@@ -16116,7 +16116,7 @@
         <v>1.84</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.66</v>
+        <v>1.78</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -16286,10 +16286,10 @@
         <v>3.8</v>
       </c>
       <c r="I82" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J82" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K82" t="n">
         <v>3.75</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -16474,16 +16474,16 @@
         <v>2</v>
       </c>
       <c r="G83" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H83" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I83" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J83" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K83" t="n">
         <v>3.6</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -16862,19 +16862,19 @@
         <v>21</v>
       </c>
       <c r="G85" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="H85" t="n">
         <v>1.13</v>
       </c>
       <c r="I85" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J85" t="n">
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -17059,16 +17059,16 @@
         <v>2.44</v>
       </c>
       <c r="H86" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I86" t="n">
         <v>1000</v>
       </c>
       <c r="J86" t="n">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="K86" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -17247,22 +17247,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="G87" t="n">
         <v>3.35</v>
       </c>
       <c r="H87" t="n">
-        <v>2.66</v>
+        <v>2.96</v>
       </c>
       <c r="I87" t="n">
         <v>4.1</v>
       </c>
       <c r="J87" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K87" t="n">
-        <v>5.4</v>
+        <v>3.8</v>
       </c>
       <c r="L87" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G88" t="n">
         <v>1.97</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.07</v>
+        <v>1.46</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -17641,16 +17641,16 @@
         <v>3.15</v>
       </c>
       <c r="H89" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="I89" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
       <c r="J89" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K89" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="L89" t="n">
         <v>0</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -17829,7 +17829,7 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="G90" t="n">
         <v>2.72</v>
@@ -17841,10 +17841,10 @@
         <v>5.1</v>
       </c>
       <c r="J90" t="n">
-        <v>2.28</v>
+        <v>2.88</v>
       </c>
       <c r="K90" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17859,7 +17859,7 @@
         <v>0</v>
       </c>
       <c r="P90" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="Q90" t="n">
         <v>2.26</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18605,19 +18605,19 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G94" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H94" t="n">
         <v>2.04</v>
       </c>
       <c r="I94" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J94" t="n">
-        <v>2.04</v>
+        <v>3.45</v>
       </c>
       <c r="K94" t="n">
         <v>1000</v>
@@ -18635,10 +18635,10 @@
         <v>0</v>
       </c>
       <c r="P94" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="R94" t="n">
         <v>0</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18805,7 +18805,7 @@
         <v>3.5</v>
       </c>
       <c r="H95" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="I95" t="n">
         <v>2.5</v>
@@ -18814,7 +18814,7 @@
         <v>3.3</v>
       </c>
       <c r="K95" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G96" t="n">
         <v>1.8</v>
@@ -19002,7 +19002,7 @@
         <v>5.9</v>
       </c>
       <c r="I96" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J96" t="n">
         <v>3.6</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -19193,16 +19193,16 @@
         <v>3.7</v>
       </c>
       <c r="H97" t="n">
-        <v>2.4</v>
+        <v>2.58</v>
       </c>
       <c r="I97" t="n">
         <v>3.55</v>
       </c>
       <c r="J97" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K97" t="n">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -19381,19 +19381,19 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.23</v>
+        <v>1.9</v>
       </c>
       <c r="G98" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H98" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="I98" t="n">
         <v>5.3</v>
       </c>
       <c r="J98" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="K98" t="n">
         <v>950</v>
@@ -19414,7 +19414,7 @@
         <v>1.24</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -19581,16 +19581,16 @@
         <v>5.5</v>
       </c>
       <c r="H99" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="I99" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="J99" t="n">
         <v>3.65</v>
       </c>
       <c r="K99" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19605,10 +19605,10 @@
         <v>0</v>
       </c>
       <c r="P99" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q99" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="R99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         <v>2.3</v>
       </c>
       <c r="G101" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H101" t="n">
         <v>3.5</v>
@@ -19975,10 +19975,10 @@
         <v>4.1</v>
       </c>
       <c r="J101" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K101" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -19993,10 +19993,10 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -20157,22 +20157,22 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="G102" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H102" t="n">
-        <v>2.62</v>
+        <v>2.76</v>
       </c>
       <c r="I102" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="J102" t="n">
-        <v>2.26</v>
+        <v>2.94</v>
       </c>
       <c r="K102" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="L102" t="n">
         <v>0</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -20939,10 +20939,10 @@
         <v>1.34</v>
       </c>
       <c r="H106" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I106" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J106" t="n">
         <v>5.7</v>
@@ -20963,10 +20963,10 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="R106" t="n">
         <v>0</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-24 03:45:00</t>
+          <t>2026-04-24 06:17:46</t>
         </is>
       </c>
     </row>
